--- a/data/pXRF/pXRF Standards.xlsx
+++ b/data/pXRF/pXRF Standards.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="fnrk9XEZIDuAtLnuGlQKamq7EV7X+GuDJ6W+PLNZQ5k="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="mLziQJsOPk07B2yo117S1T2PnYAZ/UajAOlGoUOePJg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>SiO2</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Cr</t>
+  </si>
+  <si>
+    <t>Cu</t>
   </si>
   <si>
     <t>Fe</t>
@@ -124,7 +127,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -141,6 +144,11 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -156,15 +164,19 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -378,7 +390,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="8.63"/>
+    <col customWidth="1" min="1" max="27" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -407,7 +419,7 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -449,15 +461,17 @@
       <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Y1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA1" s="1"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1">
         <v>1.0E-8</v>
@@ -471,64 +485,67 @@
       <c r="E2" s="1">
         <v>0.1298312194147608</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="4">
         <v>0.0</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="4">
         <v>0.0</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="4">
         <v>0.0</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="4">
         <v>0.0</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K2" s="4">
         <v>700.0</v>
       </c>
-      <c r="K2" s="3">
+      <c r="L2" s="4">
         <v>7.65</v>
       </c>
-      <c r="L2" s="3">
+      <c r="M2" s="4">
         <v>26.5</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="4">
         <v>0.0</v>
       </c>
-      <c r="N2" s="3">
+      <c r="O2" s="4">
         <v>0.0</v>
       </c>
-      <c r="O2" s="3">
+      <c r="P2" s="4">
         <v>0.0</v>
       </c>
-      <c r="P2" s="3">
+      <c r="Q2" s="4">
         <v>0.0</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="R2" s="4">
         <v>0.0</v>
       </c>
-      <c r="R2" s="3">
+      <c r="S2" s="4">
         <v>51.0</v>
       </c>
-      <c r="S2" s="3">
+      <c r="T2" s="4">
         <v>0.0</v>
       </c>
-      <c r="T2" s="3">
+      <c r="U2" s="4">
         <v>0.0</v>
       </c>
-      <c r="U2" s="3">
+      <c r="V2" s="4">
         <v>0.0</v>
       </c>
-      <c r="V2" s="3">
+      <c r="W2" s="4">
         <v>0.0</v>
       </c>
-      <c r="W2" s="3">
+      <c r="X2" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>11.57240592318852</v>
@@ -542,64 +559,67 @@
       <c r="E3" s="1">
         <v>0.2984167416022458</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>10.640720880092891</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <v>17.29117143015095</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <v>0.3546906960030964</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="4">
         <v>1.064072088009289</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="K3" s="4">
         <v>1902.4901321244977</v>
       </c>
-      <c r="K3" s="3">
+      <c r="L3" s="4">
         <v>20.715918514014064</v>
       </c>
-      <c r="L3" s="3">
+      <c r="M3" s="4">
         <v>72.0334180993975</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="4">
         <v>9.665321466084377</v>
       </c>
-      <c r="N3" s="3">
+      <c r="O3" s="4">
         <v>4.699651722041027</v>
       </c>
-      <c r="O3" s="3">
+      <c r="P3" s="4">
         <v>0.7093813920061928</v>
       </c>
-      <c r="P3" s="3">
+      <c r="Q3" s="4">
         <v>3.546906960030964</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="4">
         <v>28.37525568024771</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="4">
         <v>47.364420365968265</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="4">
         <v>4.522306374039479</v>
       </c>
-      <c r="T3" s="3">
+      <c r="U3" s="4">
         <v>0.1773453480015482</v>
       </c>
-      <c r="U3" s="3">
+      <c r="V3" s="4">
         <v>12.680192382110695</v>
       </c>
-      <c r="V3" s="3">
+      <c r="W3" s="4">
         <v>4.433633700038705</v>
       </c>
-      <c r="W3" s="3">
+      <c r="X3" s="4">
         <v>26.60180220023223</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>21.53134275154809</v>
@@ -613,64 +633,67 @@
       <c r="E4" s="1">
         <v>0.4551414018535499</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <v>20.565139219592776</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
         <v>33.418351231838265</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <v>0.6855046406530926</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="4">
         <v>2.0565139219592776</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="5">
+        <v>2.06</v>
+      </c>
+      <c r="K4" s="4">
         <v>3024.032107974147</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="4">
         <v>32.9022772000583</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="4">
         <v>114.50165824384075</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="4">
         <v>18.680001457796774</v>
       </c>
-      <c r="N4" s="3">
+      <c r="O4" s="4">
         <v>9.082936488653477</v>
       </c>
-      <c r="O4" s="3">
+      <c r="P4" s="4">
         <v>1.3710092813061852</v>
       </c>
-      <c r="P4" s="3">
+      <c r="Q4" s="4">
         <v>6.855046406530926</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="R4" s="4">
         <v>54.84037125224741</v>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="4">
         <v>43.9735774333058</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="4">
         <v>8.74018416832693</v>
       </c>
-      <c r="T4" s="3">
+      <c r="U4" s="4">
         <v>0.3427523203265463</v>
       </c>
-      <c r="U4" s="3">
+      <c r="V4" s="4">
         <v>24.50679090334806</v>
       </c>
-      <c r="V4" s="3">
+      <c r="W4" s="4">
         <v>8.568808008163657</v>
       </c>
-      <c r="W4" s="3">
+      <c r="X4" s="4">
         <v>51.41284804898194</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>27.16788331790245</v>
@@ -684,64 +707,67 @@
       <c r="E5" s="1">
         <v>0.549135826138045</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>26.532239155920255</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <v>43.114888628370416</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <v>0.8844079718640085</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="4">
         <v>2.653223915592026</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="K5" s="4">
         <v>3698.364126611955</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="4">
         <v>40.229378663540416</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="4">
         <v>140.0358733880421</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="4">
         <v>24.10011723329423</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="4">
         <v>11.718405627198113</v>
       </c>
-      <c r="O5" s="3">
+      <c r="P5" s="4">
         <v>1.768815943728017</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="4">
         <v>8.844079718640085</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="4">
         <v>70.75263774912068</v>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="4">
         <v>41.934818288393906</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="4">
         <v>11.276201641266109</v>
       </c>
-      <c r="T5" s="3">
+      <c r="U5" s="4">
         <v>0.4422039859320043</v>
       </c>
-      <c r="U5" s="3">
+      <c r="V5" s="4">
         <v>31.617584994138305</v>
       </c>
-      <c r="V5" s="3">
+      <c r="W5" s="4">
         <v>11.055099648300107</v>
       </c>
-      <c r="W5" s="3">
+      <c r="X5" s="4">
         <v>66.33059788980064</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1">
         <v>32.56835057314392</v>
@@ -755,64 +781,67 @@
       <c r="E6" s="1">
         <v>0.6430910649829996</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>32.50813449023863</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>52.82571854663778</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <v>1.0836044830079543</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <v>3.2508134490238634</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="K6" s="4">
         <v>4373.690098517717</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="4">
         <v>47.56728014280552</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="4">
         <v>165.60772550614612</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="4">
         <v>29.528222161966756</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="4">
         <v>14.357759399855395</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="4">
         <v>2.1672089660159086</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="4">
         <v>10.836044830079546</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="4">
         <v>86.68835864063637</v>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="4">
         <v>39.89305404916847</v>
       </c>
-      <c r="S6" s="3">
+      <c r="T6" s="4">
         <v>13.815957158351418</v>
       </c>
-      <c r="T6" s="3">
+      <c r="U6" s="4">
         <v>0.5418022415039772</v>
       </c>
-      <c r="U6" s="3">
+      <c r="V6" s="4">
         <v>38.73886026753437</v>
       </c>
-      <c r="V6" s="3">
+      <c r="W6" s="4">
         <v>13.54505603759943</v>
       </c>
-      <c r="W6" s="3">
+      <c r="X6" s="4">
         <v>81.27033622559658</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1">
         <v>55.45415549927045</v>
@@ -826,64 +855,67 @@
       <c r="E7" s="1">
         <v>1.0901517960159777</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>61.0983567317799</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="4">
         <v>99.28482968914233</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <v>2.03661189105933</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="4">
         <v>6.10983567317799</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="5">
+        <v>6.11</v>
+      </c>
+      <c r="K7" s="4">
         <v>7604.623463663893</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="4">
         <v>82.67369053689806</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="4">
         <v>287.9500515147415</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="4">
         <v>55.49767403136674</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="4">
         <v>26.98510755653612</v>
       </c>
-      <c r="O7" s="3">
+      <c r="P7" s="4">
         <v>4.07322378211866</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="4">
         <v>20.3661189105933</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="4">
         <v>162.9289512847464</v>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="4">
         <v>30.12472811664187</v>
       </c>
-      <c r="S7" s="3">
+      <c r="T7" s="4">
         <v>25.96680161100646</v>
       </c>
-      <c r="T7" s="3">
+      <c r="U7" s="4">
         <v>1.018305945529665</v>
       </c>
-      <c r="U7" s="3">
+      <c r="V7" s="4">
         <v>72.80887510537106</v>
       </c>
-      <c r="V7" s="3">
+      <c r="W7" s="4">
         <v>25.457648638241626</v>
       </c>
-      <c r="W7" s="3">
+      <c r="X7" s="4">
         <v>152.74589182944976</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1">
         <v>64.44973414710806</v>
@@ -897,64 +929,67 @@
       <c r="E8" s="1">
         <v>1.2914356105917844</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>74.05531612889952</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="4">
         <v>120.33988870946172</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="4">
         <v>2.4685105376299843</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="4">
         <v>7.405531612889953</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="5">
+        <v>7.41</v>
+      </c>
+      <c r="K8" s="4">
         <v>9068.867850200053</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="4">
         <v>98.58375692994454</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="4">
         <v>343.3950402682492</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="4">
         <v>67.26691215041707</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="4">
         <v>32.70776462359729</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="4">
         <v>4.937021075259969</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="4">
         <v>24.685105376299845</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="4">
         <v>197.48084301039876</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="4">
         <v>25.697766989292663</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="4">
         <v>31.4735093547823</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="4">
         <v>1.2342552688149921</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="4">
         <v>88.24925172027193</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="4">
         <v>30.856381720374802</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="4">
         <v>185.13829032224882</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1">
         <v>73.79532837411446</v>
@@ -968,64 +1003,67 @@
       <c r="E9" s="1">
         <v>1.5190496457729301</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>88.77100462641133</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="4">
         <v>144.25288251791838</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="4">
         <v>2.959033487547044</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="4">
         <v>8.877100462641131</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="5">
+        <v>8.88</v>
+      </c>
+      <c r="K9" s="4">
         <v>10731.863281156366</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="4">
         <v>116.65339609751423</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="4">
         <v>406.36592396385174</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="4">
         <v>80.63366253565694</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="4">
         <v>39.207193709998336</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="4">
         <v>5.918066975094088</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="4">
         <v>29.59033487547044</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="4">
         <v>236.72267900376352</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="4">
         <v>20.669906752642802</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="4">
         <v>37.727676966224806</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="4">
         <v>1.479516743773522</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="4">
         <v>105.78544717980681</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="4">
         <v>36.98791859433805</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="4">
         <v>221.9275115660283</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1">
         <v>78.81702815167452</v>
@@ -1039,64 +1077,67 @@
       <c r="E10" s="1">
         <v>1.6501081375788493</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>97.27509100364011</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <v>158.0720228809152</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <v>3.2425030334546703</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="4">
         <v>9.727509100364012</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="5">
+        <v>9.73</v>
+      </c>
+      <c r="K10" s="4">
         <v>11692.895909169696</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="4">
         <v>127.09570549488643</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="4">
         <v>442.75632691974334</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="4">
         <v>88.35820766163977</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="4">
         <v>42.96316519327438</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="4">
         <v>6.485006066909341</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="4">
         <v>32.425030334546705</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="4">
         <v>259.40024267637364</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="4">
         <v>17.76434390708963</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="4">
         <v>41.341913676547044</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="4">
         <v>1.6212515167273351</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="4">
         <v>115.91948344600446</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="4">
         <v>40.53128791818338</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="4">
         <v>243.18772750910028</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1">
         <v>84.72135098496408</v>
@@ -1110,64 +1151,67 @@
       <c r="E11" s="1">
         <v>1.812908968264421</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <v>107.87048109649525</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <v>175.2895317818048</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <v>3.5956827032165086</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="4">
         <v>10.787048109649527</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="5">
+        <v>10.79</v>
+      </c>
+      <c r="K11" s="4">
         <v>12890.263284579769</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="4">
         <v>140.10596157973814</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="4">
         <v>488.09576702541926</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="4">
         <v>97.98235366264986</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="4">
         <v>47.64279581761873</v>
       </c>
-      <c r="O11" s="3">
+      <c r="P11" s="4">
         <v>7.191365406433017</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="4">
         <v>35.95682703216508</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="4">
         <v>287.65461625732064</v>
       </c>
-      <c r="R11" s="3">
+      <c r="S11" s="4">
         <v>14.144252292030783</v>
       </c>
-      <c r="S11" s="3">
+      <c r="T11" s="4">
         <v>45.844954466010485</v>
       </c>
-      <c r="T11" s="3">
+      <c r="U11" s="4">
         <v>1.7978413516082543</v>
       </c>
-      <c r="U11" s="3">
+      <c r="V11" s="4">
         <v>128.54565663999017</v>
       </c>
-      <c r="V11" s="3">
+      <c r="W11" s="4">
         <v>44.94603379020636</v>
       </c>
-      <c r="W11" s="3">
+      <c r="X11" s="4">
         <v>269.67620274123817</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>33</v>
+      <c r="A12" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="B12" s="1">
         <v>91.0406447623172</v>
@@ -1181,58 +1225,61 @@
       <c r="E12" s="1">
         <v>1.9986216402481012</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>120.0</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <v>195.0</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <v>4.0</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <v>12.0</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="K12" s="4">
         <v>14261.0</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="4">
         <v>155.0</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="4">
         <v>540.0</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="4">
         <v>109.0</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="4">
         <v>53.0</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="4">
         <v>8.0</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="4">
         <v>40.0</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="4">
         <v>320.0</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="4">
         <v>10.0</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="4">
         <v>51.0</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="4">
         <v>2.0</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="4">
         <v>143.0</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="4">
         <v>50.0</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="4">
         <v>300.0</v>
       </c>
     </row>
